--- a/Dokumenti/Udruga Alumni AXIS_Registar članova.xlsx
+++ b/Dokumenti/Udruga Alumni AXIS_Registar članova.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rektoratunist-my.sharepoint.com/personal/vzrno_unist_hr/Documents/Alumni udruga [nova]/Web stranica/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rektoratunist-my.sharepoint.com/personal/vzrno_unist_hr/Documents/Alumni udruga [nova]/Registar članova udruge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{E636E51E-33A7-4D38-AD8C-6A172962A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E09E994E-F600-410E-B920-D985FDEFA655}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{E636E51E-33A7-4D38-AD8C-6A172962A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3870CD8D-62A7-4B91-B60B-AC8C050DD140}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Popis članova" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="114">
   <si>
     <t>Ime i prezime člana</t>
   </si>
@@ -287,6 +287,99 @@
   <si>
     <t>Alumni AXIS Split
 Popis članova</t>
+  </si>
+  <si>
+    <t>17.07.1994.</t>
+  </si>
+  <si>
+    <t>+385 (0)92 2874 491</t>
+  </si>
+  <si>
+    <t>orlic17@gmail.com</t>
+  </si>
+  <si>
+    <t>11.07.2018.</t>
+  </si>
+  <si>
+    <t>Stipan Tabak</t>
+  </si>
+  <si>
+    <t>15.01.1999.</t>
+  </si>
+  <si>
+    <t>+385 (0)97 7011 878</t>
+  </si>
+  <si>
+    <t>stipantabak6@gmail.com</t>
+  </si>
+  <si>
+    <t>2025.</t>
+  </si>
+  <si>
+    <t>16.12.2025.</t>
+  </si>
+  <si>
+    <t>Miško Dedić</t>
+  </si>
+  <si>
+    <t>03.07.1999.</t>
+  </si>
+  <si>
+    <t>+387 63104124 / +385 (0)99 7665 388</t>
+  </si>
+  <si>
+    <t>dedic.misko@gmail.com</t>
+  </si>
+  <si>
+    <t>2024.</t>
+  </si>
+  <si>
+    <t>Marijana Šušnja</t>
+  </si>
+  <si>
+    <t>21.11.1996.</t>
+  </si>
+  <si>
+    <t>+385 (0)91 5677 574</t>
+  </si>
+  <si>
+    <t>msusnja996@gmail.com</t>
+  </si>
+  <si>
+    <t>23.09.2020.</t>
+  </si>
+  <si>
+    <t>27.12.2025.</t>
+  </si>
+  <si>
+    <t>Zvonimir Buterin</t>
+  </si>
+  <si>
+    <t>29.02.1996.</t>
+  </si>
+  <si>
+    <t>+385 (0)91 7263 189</t>
+  </si>
+  <si>
+    <t>zvonimir.buterin96@gmail.com</t>
+  </si>
+  <si>
+    <t>15.09.2021.</t>
+  </si>
+  <si>
+    <t>Tea Bošnjak</t>
+  </si>
+  <si>
+    <t>16.06.2000.</t>
+  </si>
+  <si>
+    <t>+385 (0)97 6260 968</t>
+  </si>
+  <si>
+    <t>tea.bosnjak01@gmail.com</t>
+  </si>
+  <si>
+    <t>02.01.2026.</t>
   </si>
 </sst>
 </file>
@@ -409,35 +502,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -449,7 +542,49 @@
     <cellStyle name="Telefonski broj" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="18">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -498,10 +633,10 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Membership List" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Membership List" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -584,21 +719,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Popis" displayName="Popis" ref="A2:L16" totalsRowShown="0">
-  <autoFilter ref="A2:L16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Popis" displayName="Popis" ref="A2:L20" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A2:L20" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ime i prezime člana"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Datum rođenja"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="OIB"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Broj telefona/mobitela"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="E-mail adresa"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Naziv fakulteta"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Smjer / studij"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Godina završetka"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Stečena titula / zvanje"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Kategorija članstva"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Datum pristupanja"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Napomene"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ime i prezime člana" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Datum rođenja" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="OIB" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Broj telefona/mobitela" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="E-mail adresa" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Naziv fakulteta" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Smjer / studij" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Godina završetka" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Stečena titula / zvanje" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Kategorija članstva" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Datum pristupanja" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Napomene" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="Membership List" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -900,14 +1035,14 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.625" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.125" customWidth="1"/>
@@ -918,439 +1053,666 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>30860281169</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>58938067412</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4">
         <v>58203030011</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="F6" s="3" t="s">
+      <c r="D6" s="5"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
         <v>85352122772</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>93080236525</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>54095407001</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>90861466691</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="4" t="s">
         <v>53</v>
       </c>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>17370716054</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>53861670380</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>86222903729</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="4" t="s">
         <v>53</v>
       </c>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>46997326768</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="4">
+        <v>74972083337</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="4">
+        <v>89140335785</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="4">
+        <v>75736149890</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="4">
+        <v>90481324669</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="4">
+        <v>42548814438</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1379,15 +1741,21 @@
     <hyperlink ref="E13" r:id="rId7" xr:uid="{A38F593D-602A-4A6A-87EF-1542812439DC}"/>
     <hyperlink ref="E14" r:id="rId8" xr:uid="{78DF1660-E27F-4A58-B747-9FCB7AB84FA7}"/>
     <hyperlink ref="E15" r:id="rId9" xr:uid="{938B067A-3A46-44F0-AA7D-E35904CB90BF}"/>
+    <hyperlink ref="E5" r:id="rId10" xr:uid="{493A0593-B966-42CB-B9A0-402B07F85365}"/>
+    <hyperlink ref="E16" r:id="rId11" xr:uid="{5940DE71-2DA1-46D0-AC36-BA6538B2A67B}"/>
+    <hyperlink ref="E17" r:id="rId12" xr:uid="{B0821790-D9B7-44E1-B515-62A7AF38F59B}"/>
+    <hyperlink ref="E18" r:id="rId13" xr:uid="{FBD19E91-7109-4C4C-A5B2-3822DABE85EE}"/>
+    <hyperlink ref="E19" r:id="rId14" xr:uid="{5CE8067F-4D4E-4F97-A6B2-89A0816108E2}"/>
+    <hyperlink ref="E20" r:id="rId15" xr:uid="{256FD13D-3226-451F-9FA9-A4601BD3370B}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId10"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId16"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>